--- a/data/trans_orig/P19F$mañana-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P19F$mañana-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el momento del día en que acostumbra a cepillarse los dientes (multirrespuesta) en 2016</t>
+          <t>Población según el momento del día en que acostumbra a cepillarse los dientes (multirrespuesta) en 2016 (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>84254</t>
+          <t>84209</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>112577</t>
+          <t>113821</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>88119</t>
+          <t>89030</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>114504</t>
+          <t>113206</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>182766</t>
+          <t>181874</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>221565</t>
+          <t>218508</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>64,05%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30045</t>
+          <t>29819</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54632</t>
+          <t>54774</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33174</t>
+          <t>33518</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56113</t>
+          <t>56758</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69431</t>
+          <t>69957</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>103562</t>
+          <t>102115</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>103312</t>
+          <t>104270</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>128782</t>
+          <t>130275</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>105081</t>
+          <t>106930</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>128752</t>
+          <t>129892</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>218075</t>
+          <t>217530</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>252668</t>
+          <t>253176</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,22%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>98700</t>
+          <t>97970</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>130402</t>
+          <t>131798</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>91980</t>
+          <t>90693</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>123574</t>
+          <t>120440</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>196519</t>
+          <t>199856</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>241697</t>
+          <t>245521</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>50,09%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>70016</t>
+          <t>68554</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>100844</t>
+          <t>100492</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>59872</t>
+          <t>60520</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>87974</t>
+          <t>90334</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>137258</t>
+          <t>138576</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>180466</t>
+          <t>181436</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>37,01%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>120772</t>
+          <t>122323</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>154349</t>
+          <t>153270</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>138872</t>
+          <t>138707</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>170112</t>
+          <t>169166</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>270052</t>
+          <t>269679</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>313496</t>
+          <t>314998</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>64,26%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>74910</t>
+          <t>73986</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>97089</t>
+          <t>96540</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59014</t>
+          <t>58164</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76797</t>
+          <t>75430</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>139006</t>
+          <t>139088</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>166119</t>
+          <t>167161</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>71,04%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40085</t>
+          <t>39600</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61651</t>
+          <t>61353</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13952</t>
+          <t>13423</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30003</t>
+          <t>29306</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58453</t>
+          <t>56761</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>85797</t>
+          <t>83254</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>35,38%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>99554</t>
+          <t>98328</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>117366</t>
+          <t>116981</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>78467</t>
+          <t>78299</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>91622</t>
+          <t>90680</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>180908</t>
+          <t>182211</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>203833</t>
+          <t>204734</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>87,0%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82145</t>
+          <t>80850</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>112105</t>
+          <t>111636</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>115665</t>
+          <t>114341</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>145501</t>
+          <t>145195</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>203818</t>
+          <t>206319</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>247186</t>
+          <t>248670</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>57,14%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39933</t>
+          <t>40068</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66556</t>
+          <t>66132</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39316</t>
+          <t>40059</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65911</t>
+          <t>66810</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>86518</t>
+          <t>85555</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>123197</t>
+          <t>122804</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,22%</t>
         </is>
       </c>
     </row>
@@ -1985,12 +1985,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>149612</t>
+          <t>148775</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>173646</t>
+          <t>173510</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>169962</t>
+          <t>168250</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>195664</t>
+          <t>192909</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2035,12 +2035,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2055,12 +2055,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>326264</t>
+          <t>327033</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>360237</t>
+          <t>361817</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>83,14%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>5535</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18205</t>
+          <t>17921</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14588</t>
+          <t>14773</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31217</t>
+          <t>31884</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23329</t>
+          <t>23003</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44966</t>
+          <t>44310</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59653</t>
+          <t>61005</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82887</t>
+          <t>83366</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64702</t>
+          <t>65226</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>89107</t>
+          <t>87505</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>132568</t>
+          <t>131226</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>164872</t>
+          <t>165136</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,29%</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>129579</t>
+          <t>130176</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>141182</t>
+          <t>141688</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2363,12 +2363,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>133962</t>
+          <t>133655</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>144251</t>
+          <t>144313</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2378,12 +2378,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2398,12 +2398,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>267388</t>
+          <t>267992</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>283460</t>
+          <t>283673</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32201</t>
+          <t>31963</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>54298</t>
+          <t>53813</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33120</t>
+          <t>33170</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55939</t>
+          <t>56281</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>72295</t>
+          <t>70070</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>105029</t>
+          <t>101831</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>31,33%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41637</t>
+          <t>42876</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>65196</t>
+          <t>66154</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>69897</t>
+          <t>68925</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>95881</t>
+          <t>95843</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>116844</t>
+          <t>116691</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>153866</t>
+          <t>154948</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,67%</t>
         </is>
       </c>
     </row>
@@ -2671,12 +2671,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>105035</t>
+          <t>104694</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>124670</t>
+          <t>124546</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,12 +2686,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>130701</t>
+          <t>130611</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>152420</t>
+          <t>151801</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,12 +2721,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>244532</t>
+          <t>244727</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>271814</t>
+          <t>273096</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>84,01%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>106465</t>
+          <t>105603</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>143625</t>
+          <t>144061</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>118488</t>
+          <t>117945</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>156398</t>
+          <t>157464</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>233997</t>
+          <t>234658</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>288686</t>
+          <t>290371</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>39,17%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>85150</t>
+          <t>85567</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>122088</t>
+          <t>122008</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>96907</t>
+          <t>96677</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>133209</t>
+          <t>132871</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>194952</t>
+          <t>191471</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>243403</t>
+          <t>241974</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,64%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>274727</t>
+          <t>276697</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>309699</t>
+          <t>312353</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>263251</t>
+          <t>263337</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>296017</t>
+          <t>296071</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>551995</t>
+          <t>551238</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>598283</t>
+          <t>596444</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,45%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>134348</t>
+          <t>134912</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>172523</t>
+          <t>171231</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>152549</t>
+          <t>154201</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>192592</t>
+          <t>191241</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>302210</t>
+          <t>298298</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>354294</t>
+          <t>351270</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,25%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>76104</t>
+          <t>76433</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>107620</t>
+          <t>109471</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>77734</t>
+          <t>78761</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>112871</t>
+          <t>111999</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>162041</t>
+          <t>161191</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>206367</t>
+          <t>210136</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,86%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>300554</t>
+          <t>299500</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>315918</t>
+          <t>315556</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>286140</t>
+          <t>288277</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>310372</t>
+          <t>310789</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>594281</t>
+          <t>595327</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>621441</t>
+          <t>621908</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,28%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>687665</t>
+          <t>678823</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>768305</t>
+          <t>766106</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>740774</t>
+          <t>740350</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>825126</t>
+          <t>828265</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1455044</t>
+          <t>1450680</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1575069</t>
+          <t>1567574</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,52%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>511174</t>
+          <t>508029</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>586444</t>
+          <t>588603</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>519259</t>
+          <t>522131</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>596831</t>
+          <t>603307</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1042418</t>
+          <t>1046212</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1157740</t>
+          <t>1160166</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,95%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1344079</t>
+          <t>1346408</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1415670</t>
+          <t>1417911</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1374368</t>
+          <t>1369135</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1438597</t>
+          <t>1436644</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2738106</t>
+          <t>2737006</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2840362</t>
+          <t>2840885</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19F$mañana-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P19F$mañana-Provincia-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>84209</t>
+          <t>86961</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>113821</t>
+          <t>113999</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>89030</t>
+          <t>90120</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>113206</t>
+          <t>113582</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>181874</t>
+          <t>182932</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>218508</t>
+          <t>219387</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>64,31%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29819</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54774</t>
+          <t>54092</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33518</t>
+          <t>33995</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56758</t>
+          <t>56590</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69957</t>
+          <t>69051</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>102115</t>
+          <t>102518</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,05%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>104270</t>
+          <t>103961</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>130275</t>
+          <t>130656</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>106930</t>
+          <t>106209</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>129892</t>
+          <t>129235</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>217530</t>
+          <t>216832</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>253176</t>
+          <t>253405</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,28%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>97970</t>
+          <t>100143</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>131798</t>
+          <t>130084</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>90693</t>
+          <t>91676</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>120440</t>
+          <t>122854</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>199856</t>
+          <t>199343</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>245521</t>
+          <t>243328</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>49,64%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68554</t>
+          <t>70122</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>100492</t>
+          <t>99801</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60520</t>
+          <t>61303</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90334</t>
+          <t>90559</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>138576</t>
+          <t>140109</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>181436</t>
+          <t>180894</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,9%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>122323</t>
+          <t>121620</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>153270</t>
+          <t>153448</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>138707</t>
+          <t>138911</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>169166</t>
+          <t>168647</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>269679</t>
+          <t>270459</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>314998</t>
+          <t>313885</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,03%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>73986</t>
+          <t>75150</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96540</t>
+          <t>96819</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58164</t>
+          <t>58757</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75430</t>
+          <t>75787</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>139088</t>
+          <t>136843</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>167161</t>
+          <t>166678</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>70,83%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39600</t>
+          <t>40156</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61353</t>
+          <t>62438</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13423</t>
+          <t>13283</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29306</t>
+          <t>29894</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56761</t>
+          <t>56650</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>83254</t>
+          <t>84492</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,91%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>98328</t>
+          <t>99039</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>116981</t>
+          <t>117153</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>78299</t>
+          <t>77971</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>90680</t>
+          <t>91087</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>182211</t>
+          <t>182605</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>204734</t>
+          <t>204598</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,95%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80850</t>
+          <t>81909</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111636</t>
+          <t>110302</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>114341</t>
+          <t>114270</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>145195</t>
+          <t>145998</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>206319</t>
+          <t>203718</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>248670</t>
+          <t>248452</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>57,09%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40068</t>
+          <t>40168</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66132</t>
+          <t>65356</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40059</t>
+          <t>39728</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>66810</t>
+          <t>66133</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>85555</t>
+          <t>87413</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>122804</t>
+          <t>124316</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -1985,12 +1985,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>148775</t>
+          <t>148880</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>173510</t>
+          <t>173312</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>168250</t>
+          <t>170112</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>192909</t>
+          <t>195084</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2035,12 +2035,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2055,12 +2055,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>327033</t>
+          <t>326964</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>361817</t>
+          <t>362758</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,36%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17921</t>
+          <t>17718</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14773</t>
+          <t>15271</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31884</t>
+          <t>32808</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23003</t>
+          <t>22606</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44310</t>
+          <t>44566</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61005</t>
+          <t>59606</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>83366</t>
+          <t>83308</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>65226</t>
+          <t>65064</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>87505</t>
+          <t>88790</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>131226</t>
+          <t>132536</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>165136</t>
+          <t>165702</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,48%</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>130176</t>
+          <t>130212</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>141688</t>
+          <t>141596</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2363,12 +2363,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>133655</t>
+          <t>131865</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>144313</t>
+          <t>144145</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2378,12 +2378,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2398,12 +2398,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>267992</t>
+          <t>268296</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>283673</t>
+          <t>283627</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31963</t>
+          <t>32701</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>53813</t>
+          <t>54811</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33170</t>
+          <t>34078</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56281</t>
+          <t>57060</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>70070</t>
+          <t>71840</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101831</t>
+          <t>103507</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,84%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42876</t>
+          <t>42511</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66154</t>
+          <t>65533</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>68925</t>
+          <t>68809</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>95843</t>
+          <t>95799</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>116691</t>
+          <t>118856</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>154948</t>
+          <t>156071</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>48,01%</t>
         </is>
       </c>
     </row>
@@ -2671,12 +2671,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>104694</t>
+          <t>105940</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>124546</t>
+          <t>124955</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,12 +2686,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>130611</t>
+          <t>131059</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>151801</t>
+          <t>153020</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,12 +2721,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>244727</t>
+          <t>243832</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>273096</t>
+          <t>271870</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,64%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>105603</t>
+          <t>104271</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>144061</t>
+          <t>143959</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>117945</t>
+          <t>119894</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>157464</t>
+          <t>157588</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>234658</t>
+          <t>233309</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>290371</t>
+          <t>288056</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>38,85%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>85567</t>
+          <t>87263</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>122008</t>
+          <t>124255</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>96677</t>
+          <t>97094</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>132871</t>
+          <t>132753</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>191471</t>
+          <t>193944</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>241974</t>
+          <t>247694</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>276697</t>
+          <t>275950</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>312353</t>
+          <t>310510</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>263337</t>
+          <t>264209</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>296071</t>
+          <t>295996</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>551238</t>
+          <t>546954</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>596444</t>
+          <t>596661</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,48%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>134912</t>
+          <t>135337</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>171231</t>
+          <t>171324</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>154201</t>
+          <t>151993</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>191241</t>
+          <t>191759</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>298298</t>
+          <t>300773</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>351270</t>
+          <t>354939</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>53,81%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>76433</t>
+          <t>74104</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>109471</t>
+          <t>107688</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>78761</t>
+          <t>78445</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>111999</t>
+          <t>111555</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>161191</t>
+          <t>160867</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>210136</t>
+          <t>206901</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,36%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>299500</t>
+          <t>298919</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>315556</t>
+          <t>315532</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>288277</t>
+          <t>286689</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>310789</t>
+          <t>310683</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>595327</t>
+          <t>592652</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>621908</t>
+          <t>621370</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,2%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>678823</t>
+          <t>688651</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>766106</t>
+          <t>772357</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>740350</t>
+          <t>741817</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>828265</t>
+          <t>827572</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1450680</t>
+          <t>1450668</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1567574</t>
+          <t>1565117</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,45%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>508029</t>
+          <t>505745</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>588603</t>
+          <t>589137</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>522131</t>
+          <t>519547</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>603307</t>
+          <t>596318</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1046212</t>
+          <t>1054609</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1160166</t>
+          <t>1162218</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,01%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1346408</t>
+          <t>1345093</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1417911</t>
+          <t>1415764</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1369135</t>
+          <t>1370750</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1436644</t>
+          <t>1440189</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2737006</t>
+          <t>2738440</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2840885</t>
+          <t>2840308</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,66%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19F$mañana-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P19F$mañana-Provincia-trans_orig.xlsx
@@ -828,112 +828,112 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>110</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41139</t>
+          <t>117401</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>103961</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54092</t>
+          <t>130656</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>112</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>44123</t>
+          <t>118999</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33995</t>
+          <t>106209</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56590</t>
+          <t>129235</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>222</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>85262</t>
+          <t>236400</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69051</t>
+          <t>216832</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>102518</t>
+          <t>253405</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>74,28%</t>
         </is>
       </c>
     </row>
@@ -941,112 +941,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>117401</t>
+          <t>41139</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>103961</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>130656</t>
+          <t>54092</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>118999</t>
+          <t>44123</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>106209</t>
+          <t>33995</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>129235</t>
+          <t>56590</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>78</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>236400</t>
+          <t>85262</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>216832</t>
+          <t>69051</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>253405</t>
+          <t>102518</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>30,05%</t>
         </is>
       </c>
     </row>
@@ -1171,112 +1171,112 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>132</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>84882</t>
+          <t>137559</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>70122</t>
+          <t>121620</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>99801</t>
+          <t>153448</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>141</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>74602</t>
+          <t>154504</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61303</t>
+          <t>138911</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90559</t>
+          <t>168647</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>273</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>159484</t>
+          <t>292063</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>140109</t>
+          <t>270459</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>180894</t>
+          <t>313885</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>64,03%</t>
         </is>
       </c>
     </row>
@@ -1284,112 +1284,112 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>137559</t>
+          <t>84882</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>121620</t>
+          <t>70122</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>153448</t>
+          <t>99801</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>154504</t>
+          <t>74602</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>138911</t>
+          <t>61303</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>168647</t>
+          <t>90559</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>148</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>292063</t>
+          <t>159484</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>270459</t>
+          <t>140109</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>313885</t>
+          <t>180894</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>36,9%</t>
         </is>
       </c>
     </row>
@@ -1514,112 +1514,112 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50173</t>
+          <t>108985</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40156</t>
+          <t>99039</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62438</t>
+          <t>117153</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20435</t>
+          <t>85580</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13283</t>
+          <t>77971</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29894</t>
+          <t>91087</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>200</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>70608</t>
+          <t>194565</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56650</t>
+          <t>182605</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>84492</t>
+          <t>204598</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>86,95%</t>
         </is>
       </c>
     </row>
@@ -1627,112 +1627,112 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>54</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>108985</t>
+          <t>50173</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>99039</t>
+          <t>40156</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>117153</t>
+          <t>62438</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>85580</t>
+          <t>20435</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>77971</t>
+          <t>13283</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>91087</t>
+          <t>29894</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>74</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>194565</t>
+          <t>70608</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>182605</t>
+          <t>56650</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>204598</t>
+          <t>84492</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>35,91%</t>
         </is>
       </c>
     </row>
@@ -1857,112 +1857,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>153</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>51942</t>
+          <t>162268</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40168</t>
+          <t>148880</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>65356</t>
+          <t>173312</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>171</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>51941</t>
+          <t>182803</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39728</t>
+          <t>170112</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>66133</t>
+          <t>195084</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>324</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>103882</t>
+          <t>345070</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>87413</t>
+          <t>326964</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>124316</t>
+          <t>362758</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>83,36%</t>
         </is>
       </c>
     </row>
@@ -1970,112 +1970,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>162268</t>
+          <t>51942</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>148880</t>
+          <t>40168</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>173312</t>
+          <t>65356</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>182803</t>
+          <t>51941</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>170112</t>
+          <t>39728</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>195084</t>
+          <t>66133</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>96</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>345070</t>
+          <t>103882</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>326964</t>
+          <t>87413</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>362758</t>
+          <t>124316</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -2200,112 +2200,112 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>139</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>72008</t>
+          <t>136894</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59606</t>
+          <t>130212</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>83308</t>
+          <t>141596</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>143</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>76842</t>
+          <t>140060</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>65064</t>
+          <t>131865</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>88790</t>
+          <t>144145</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>282</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>148850</t>
+          <t>276952</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>132536</t>
+          <t>268296</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>165702</t>
+          <t>283627</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -2313,112 +2313,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>136894</t>
+          <t>72008</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>130212</t>
+          <t>59606</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>141596</t>
+          <t>83308</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>79</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>140060</t>
+          <t>76842</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>131865</t>
+          <t>65064</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>144145</t>
+          <t>88790</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>152</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>276952</t>
+          <t>148850</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>268296</t>
+          <t>132536</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>283627</t>
+          <t>165702</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>56,48%</t>
         </is>
       </c>
     </row>
@@ -2543,112 +2543,112 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>114</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>53174</t>
+          <t>115942</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42511</t>
+          <t>105940</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>65533</t>
+          <t>124955</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>140</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>82232</t>
+          <t>142900</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>68809</t>
+          <t>131059</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>95799</t>
+          <t>153020</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>254</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>135406</t>
+          <t>258842</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>118856</t>
+          <t>243832</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>156071</t>
+          <t>271870</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>83,64%</t>
         </is>
       </c>
     </row>
@@ -2656,112 +2656,112 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>115942</t>
+          <t>53174</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>105940</t>
+          <t>42511</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>124955</t>
+          <t>65533</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>142900</t>
+          <t>82232</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>131059</t>
+          <t>68809</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>153020</t>
+          <t>95799</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>134</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>258842</t>
+          <t>135406</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>243832</t>
+          <t>118856</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>271870</t>
+          <t>156071</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>48,01%</t>
         </is>
       </c>
     </row>
@@ -2886,112 +2886,112 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>262</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>103086</t>
+          <t>294549</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>87263</t>
+          <t>275950</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>124255</t>
+          <t>310510</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>264</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>114519</t>
+          <t>280895</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>97094</t>
+          <t>264209</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>132753</t>
+          <t>295996</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>526</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>217605</t>
+          <t>575444</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>193944</t>
+          <t>546954</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>247694</t>
+          <t>596661</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>80,48%</t>
         </is>
       </c>
     </row>
@@ -2999,112 +2999,112 @@
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>294549</t>
+          <t>103086</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>275950</t>
+          <t>87263</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>310510</t>
+          <t>124255</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>108</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>280895</t>
+          <t>114519</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>264209</t>
+          <t>97094</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>295996</t>
+          <t>132753</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>199</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>575444</t>
+          <t>217605</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>546954</t>
+          <t>193944</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>596661</t>
+          <t>247694</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -3229,112 +3229,112 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>91180</t>
+          <t>309117</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>74104</t>
+          <t>298919</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>107688</t>
+          <t>315532</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>276</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>93868</t>
+          <t>300117</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>78445</t>
+          <t>286689</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>111555</t>
+          <t>310683</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>576</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>185048</t>
+          <t>609234</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>160867</t>
+          <t>592652</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>206901</t>
+          <t>621370</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>94,2%</t>
         </is>
       </c>
     </row>
@@ -3342,112 +3342,112 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>309117</t>
+          <t>91180</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>298919</t>
+          <t>74104</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>315532</t>
+          <t>107688</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>88</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>300117</t>
+          <t>93868</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>286689</t>
+          <t>78445</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>310683</t>
+          <t>111555</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>176</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>609234</t>
+          <t>185048</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>592652</t>
+          <t>160867</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>621370</t>
+          <t>206901</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>31,36%</t>
         </is>
       </c>
     </row>
@@ -3572,112 +3572,112 @@
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>547584</t>
+          <t>1382714</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>505745</t>
+          <t>1345093</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>589137</t>
+          <t>1415764</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>558561</t>
+          <t>1405857</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>519547</t>
+          <t>1370750</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>596318</t>
+          <t>1440189</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1106145</t>
+          <t>2788572</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1054609</t>
+          <t>2738440</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1162218</t>
+          <t>2840308</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>80,66%</t>
         </is>
       </c>
     </row>
@@ -3685,112 +3685,112 @@
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>521</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1382714</t>
+          <t>547584</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1345093</t>
+          <t>505745</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1415764</t>
+          <t>589137</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>536</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1405857</t>
+          <t>558561</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1370750</t>
+          <t>519547</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1440189</t>
+          <t>596318</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>2788572</t>
+          <t>1106145</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2738440</t>
+          <t>1054609</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2840308</t>
+          <t>1162218</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>33,01%</t>
         </is>
       </c>
     </row>
